--- a/quiz/간단교육_퀴즈_문항집.xlsx
+++ b/quiz/간단교육_퀴즈_문항집.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3554" uniqueCount="1670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3554" uniqueCount="1669">
   <si>
     <t xml:space="preserve">간단교육 퀴즈 문항집</t>
   </si>
@@ -16982,7 +16982,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">어린이 생활안전 &gt; 교통안전 &gt; 어린이 보행안전 &gt; 어린이 보행사고 예방을 위한 안전수칙 (도로교통법 제10조제2항)</t>
+    <t xml:space="preserve">찾기쉬운 생활법령정보 - 어린이 보행사고 예방을 위한 안전수칙(도로교통법 제10조제2항)</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=1</t>
@@ -17047,9 +17047,6 @@
       </rPr>
       <t xml:space="preserve">.</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">안전 배움터 &gt; 도로·교통 &gt; 어린이보호구역 교통안전수칙</t>
   </si>
   <si>
     <r>
@@ -39583,7 +39580,7 @@
         <v>25</v>
       </c>
       <c r="G6" s="34" t="s">
-        <v>1246</v>
+        <v>1234</v>
       </c>
       <c r="H6" s="35" t="s">
         <v>1235</v>
@@ -39597,13 +39594,13 @@
         <v>1231</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="D7" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="F7" s="29" t="s">
         <v>25</v>
@@ -39623,13 +39620,13 @@
         <v>1231</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="D8" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="F8" s="29" t="s">
         <v>25</v>
@@ -39649,13 +39646,13 @@
         <v>1231</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="D9" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="F9" s="29" t="s">
         <v>25</v>
@@ -39675,22 +39672,22 @@
         <v>1231</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="D10" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="F10" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G10" s="34" t="s">
+        <v>1254</v>
+      </c>
+      <c r="H10" s="35" t="s">
         <v>1255</v>
-      </c>
-      <c r="H10" s="35" t="s">
-        <v>1256</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39701,22 +39698,22 @@
         <v>1231</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="D11" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="F11" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39727,22 +39724,22 @@
         <v>1231</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="D12" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E12" s="29" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F12" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39753,22 +39750,22 @@
         <v>1231</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D13" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E13" s="29" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="F13" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G13" s="34" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H13" s="35" t="s">
         <v>1265</v>
-      </c>
-      <c r="H13" s="35" t="s">
-        <v>1266</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39779,22 +39776,22 @@
         <v>1231</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="D14" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="F14" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G14" s="34" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H14" s="35" t="s">
         <v>1269</v>
-      </c>
-      <c r="H14" s="35" t="s">
-        <v>1270</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39805,22 +39802,22 @@
         <v>1231</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="D15" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E15" s="29" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="F15" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H15" s="35" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39831,22 +39828,22 @@
         <v>1231</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="D16" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="F16" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G16" s="34" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H16" s="35" t="s">
         <v>1276</v>
-      </c>
-      <c r="H16" s="35" t="s">
-        <v>1277</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39857,22 +39854,22 @@
         <v>1231</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="D17" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="F17" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G17" s="34" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H17" s="35" t="s">
         <v>1276</v>
-      </c>
-      <c r="H17" s="35" t="s">
-        <v>1277</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39880,25 +39877,25 @@
         <v>17</v>
       </c>
       <c r="B18" s="28" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C18" s="29" t="s">
         <v>1280</v>
-      </c>
-      <c r="C18" s="29" t="s">
-        <v>1281</v>
       </c>
       <c r="D18" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="F18" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G18" s="34" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H18" s="35" t="s">
         <v>1283</v>
-      </c>
-      <c r="H18" s="35" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39906,25 +39903,25 @@
         <v>18</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="D19" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E19" s="29" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="F19" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G19" s="34" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H19" s="35" t="s">
         <v>1283</v>
-      </c>
-      <c r="H19" s="35" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39932,25 +39929,25 @@
         <v>19</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D20" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="F20" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G20" s="34" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H20" s="35" t="s">
         <v>1283</v>
-      </c>
-      <c r="H20" s="35" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39958,25 +39955,25 @@
         <v>20</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="D21" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E21" s="29" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="F21" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G21" s="34" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H21" s="35" t="s">
         <v>1283</v>
-      </c>
-      <c r="H21" s="35" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39984,25 +39981,25 @@
         <v>21</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="D22" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E22" s="29" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="F22" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G22" s="34" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H22" s="35" t="s">
         <v>1283</v>
-      </c>
-      <c r="H22" s="35" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40010,25 +40007,25 @@
         <v>22</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="D23" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E23" s="29" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="F23" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G23" s="34" t="s">
+        <v>1294</v>
+      </c>
+      <c r="H23" s="35" t="s">
         <v>1295</v>
-      </c>
-      <c r="H23" s="35" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40036,25 +40033,25 @@
         <v>23</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="D24" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E24" s="29" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="F24" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G24" s="34" t="s">
+        <v>1294</v>
+      </c>
+      <c r="H24" s="35" t="s">
         <v>1295</v>
-      </c>
-      <c r="H24" s="35" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40062,25 +40059,25 @@
         <v>24</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="D25" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E25" s="29" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="F25" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G25" s="34" t="s">
+        <v>1294</v>
+      </c>
+      <c r="H25" s="35" t="s">
         <v>1295</v>
-      </c>
-      <c r="H25" s="35" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40088,25 +40085,25 @@
         <v>25</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="D26" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E26" s="29" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="F26" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G26" s="34" t="s">
+        <v>1294</v>
+      </c>
+      <c r="H26" s="35" t="s">
         <v>1295</v>
-      </c>
-      <c r="H26" s="35" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40114,25 +40111,25 @@
         <v>26</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D27" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E27" s="29" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="F27" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G27" s="34" t="s">
+        <v>1294</v>
+      </c>
+      <c r="H27" s="35" t="s">
         <v>1295</v>
-      </c>
-      <c r="H27" s="35" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40140,25 +40137,25 @@
         <v>27</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="D28" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E28" s="29" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="F28" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G28" s="34" t="s">
+        <v>1306</v>
+      </c>
+      <c r="H28" s="35" t="s">
         <v>1307</v>
-      </c>
-      <c r="H28" s="35" t="s">
-        <v>1308</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40166,25 +40163,25 @@
         <v>28</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="D29" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E29" s="29" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="F29" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G29" s="34" t="s">
+        <v>1306</v>
+      </c>
+      <c r="H29" s="35" t="s">
         <v>1307</v>
-      </c>
-      <c r="H29" s="35" t="s">
-        <v>1308</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40192,25 +40189,25 @@
         <v>29</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="D30" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E30" s="29" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="F30" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G30" s="34" t="s">
+        <v>1306</v>
+      </c>
+      <c r="H30" s="35" t="s">
         <v>1307</v>
-      </c>
-      <c r="H30" s="35" t="s">
-        <v>1308</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40218,25 +40215,25 @@
         <v>30</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="D31" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E31" s="29" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="F31" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G31" s="34" t="s">
+        <v>1306</v>
+      </c>
+      <c r="H31" s="35" t="s">
         <v>1307</v>
-      </c>
-      <c r="H31" s="35" t="s">
-        <v>1308</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40244,25 +40241,25 @@
         <v>31</v>
       </c>
       <c r="B32" s="28" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C32" s="29" t="s">
         <v>1315</v>
-      </c>
-      <c r="C32" s="29" t="s">
-        <v>1316</v>
       </c>
       <c r="D32" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E32" s="29" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="F32" s="29" t="s">
         <v>35</v>
       </c>
       <c r="G32" s="34" t="s">
+        <v>1317</v>
+      </c>
+      <c r="H32" s="35" t="s">
         <v>1318</v>
-      </c>
-      <c r="H32" s="35" t="s">
-        <v>1319</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40270,25 +40267,25 @@
         <v>32</v>
       </c>
       <c r="B33" s="28" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C33" s="29" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="D33" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E33" s="29" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="F33" s="29" t="s">
         <v>35</v>
       </c>
       <c r="G33" s="34" t="s">
+        <v>1317</v>
+      </c>
+      <c r="H33" s="35" t="s">
         <v>1318</v>
-      </c>
-      <c r="H33" s="35" t="s">
-        <v>1319</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40296,25 +40293,25 @@
         <v>33</v>
       </c>
       <c r="B34" s="28" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="D34" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E34" s="29" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="F34" s="29" t="s">
         <v>35</v>
       </c>
       <c r="G34" s="34" t="s">
+        <v>1317</v>
+      </c>
+      <c r="H34" s="35" t="s">
         <v>1318</v>
-      </c>
-      <c r="H34" s="35" t="s">
-        <v>1319</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40322,25 +40319,25 @@
         <v>34</v>
       </c>
       <c r="B35" s="28" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="D35" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E35" s="29" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="F35" s="29" t="s">
         <v>36</v>
       </c>
       <c r="G35" s="34" t="s">
+        <v>1325</v>
+      </c>
+      <c r="H35" s="35" t="s">
         <v>1326</v>
-      </c>
-      <c r="H35" s="35" t="s">
-        <v>1327</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40348,25 +40345,25 @@
         <v>35</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="D36" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="F36" s="29" t="s">
         <v>35</v>
       </c>
       <c r="G36" s="34" t="s">
+        <v>1317</v>
+      </c>
+      <c r="H36" s="35" t="s">
         <v>1318</v>
-      </c>
-      <c r="H36" s="35" t="s">
-        <v>1319</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40374,25 +40371,25 @@
         <v>36</v>
       </c>
       <c r="B37" s="28" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D37" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E37" s="29" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="F37" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G37" s="34" t="s">
+        <v>1331</v>
+      </c>
+      <c r="H37" s="35" t="s">
         <v>1332</v>
-      </c>
-      <c r="H37" s="35" t="s">
-        <v>1333</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40400,25 +40397,25 @@
         <v>37</v>
       </c>
       <c r="B38" s="28" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="D38" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E38" s="29" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="F38" s="29" t="s">
         <v>36</v>
       </c>
       <c r="G38" s="34" t="s">
+        <v>1325</v>
+      </c>
+      <c r="H38" s="35" t="s">
         <v>1326</v>
-      </c>
-      <c r="H38" s="35" t="s">
-        <v>1327</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40426,25 +40423,25 @@
         <v>38</v>
       </c>
       <c r="B39" s="28" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D39" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="F39" s="29" t="s">
         <v>35</v>
       </c>
       <c r="G39" s="34" t="s">
+        <v>1317</v>
+      </c>
+      <c r="H39" s="35" t="s">
         <v>1318</v>
-      </c>
-      <c r="H39" s="35" t="s">
-        <v>1319</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40452,25 +40449,25 @@
         <v>39</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C40" s="39" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="D40" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="F40" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G40" s="34" t="s">
+        <v>1339</v>
+      </c>
+      <c r="H40" s="35" t="s">
         <v>1340</v>
-      </c>
-      <c r="H40" s="35" t="s">
-        <v>1341</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40478,25 +40475,25 @@
         <v>40</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C41" s="39" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D41" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E41" s="29" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="F41" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G41" s="34" t="s">
+        <v>1339</v>
+      </c>
+      <c r="H41" s="35" t="s">
         <v>1340</v>
-      </c>
-      <c r="H41" s="35" t="s">
-        <v>1341</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40504,25 +40501,25 @@
         <v>41</v>
       </c>
       <c r="B42" s="28" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D42" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E42" s="29" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="F42" s="29" t="s">
         <v>36</v>
       </c>
       <c r="G42" s="34" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H42" s="35" t="s">
         <v>1346</v>
-      </c>
-      <c r="H42" s="35" t="s">
-        <v>1347</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40530,25 +40527,25 @@
         <v>42</v>
       </c>
       <c r="B43" s="28" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D43" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E43" s="29" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="F43" s="29" t="s">
         <v>36</v>
       </c>
       <c r="G43" s="34" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H43" s="35" t="s">
         <v>1346</v>
-      </c>
-      <c r="H43" s="35" t="s">
-        <v>1347</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40556,25 +40553,25 @@
         <v>43</v>
       </c>
       <c r="B44" s="28" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D44" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E44" s="29" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="F44" s="29" t="s">
         <v>36</v>
       </c>
       <c r="G44" s="34" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H44" s="35" t="s">
         <v>1346</v>
-      </c>
-      <c r="H44" s="35" t="s">
-        <v>1347</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40582,25 +40579,25 @@
         <v>44</v>
       </c>
       <c r="B45" s="28" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C45" s="29" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D45" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E45" s="29" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="F45" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G45" s="34" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="H45" s="35" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40608,25 +40605,25 @@
         <v>45</v>
       </c>
       <c r="B46" s="28" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C46" s="29" t="s">
         <v>1355</v>
-      </c>
-      <c r="C46" s="29" t="s">
-        <v>1356</v>
       </c>
       <c r="D46" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E46" s="29" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="F46" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G46" s="34" t="s">
+        <v>1357</v>
+      </c>
+      <c r="H46" s="35" t="s">
         <v>1358</v>
-      </c>
-      <c r="H46" s="35" t="s">
-        <v>1359</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40634,25 +40631,25 @@
         <v>46</v>
       </c>
       <c r="B47" s="28" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="C47" s="29" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="D47" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E47" s="29" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F47" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G47" s="34" t="s">
+        <v>1357</v>
+      </c>
+      <c r="H47" s="35" t="s">
         <v>1358</v>
-      </c>
-      <c r="H47" s="35" t="s">
-        <v>1359</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40660,25 +40657,25 @@
         <v>47</v>
       </c>
       <c r="B48" s="28" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="C48" s="29" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="D48" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E48" s="29" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="F48" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G48" s="34" t="s">
+        <v>1357</v>
+      </c>
+      <c r="H48" s="35" t="s">
         <v>1358</v>
-      </c>
-      <c r="H48" s="35" t="s">
-        <v>1359</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40686,25 +40683,25 @@
         <v>48</v>
       </c>
       <c r="B49" s="28" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="C49" s="29" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="D49" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E49" s="29" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="F49" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G49" s="34" t="s">
+        <v>1357</v>
+      </c>
+      <c r="H49" s="35" t="s">
         <v>1358</v>
-      </c>
-      <c r="H49" s="35" t="s">
-        <v>1359</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40712,25 +40709,25 @@
         <v>49</v>
       </c>
       <c r="B50" s="28" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="C50" s="29" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D50" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E50" s="29" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="F50" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G50" s="34" t="s">
+        <v>1357</v>
+      </c>
+      <c r="H50" s="35" t="s">
         <v>1358</v>
-      </c>
-      <c r="H50" s="35" t="s">
-        <v>1359</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40738,25 +40735,25 @@
         <v>50</v>
       </c>
       <c r="B51" s="28" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="C51" s="29" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D51" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E51" s="29" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="F51" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G51" s="34" t="s">
+        <v>1306</v>
+      </c>
+      <c r="H51" s="35" t="s">
         <v>1307</v>
-      </c>
-      <c r="H51" s="35" t="s">
-        <v>1308</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40764,25 +40761,25 @@
         <v>51</v>
       </c>
       <c r="B52" s="28" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="C52" s="29" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="D52" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E52" s="29" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="F52" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G52" s="34" t="s">
+        <v>1357</v>
+      </c>
+      <c r="H52" s="35" t="s">
         <v>1358</v>
-      </c>
-      <c r="H52" s="35" t="s">
-        <v>1359</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40790,25 +40787,25 @@
         <v>52</v>
       </c>
       <c r="B53" s="28" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="C53" s="29" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="D53" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E53" s="29" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="F53" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G53" s="34" t="s">
+        <v>1373</v>
+      </c>
+      <c r="H53" s="35" t="s">
         <v>1374</v>
-      </c>
-      <c r="H53" s="35" t="s">
-        <v>1375</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40816,25 +40813,25 @@
         <v>53</v>
       </c>
       <c r="B54" s="28" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="C54" s="29" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="D54" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E54" s="29" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="F54" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G54" s="34" t="s">
+        <v>1373</v>
+      </c>
+      <c r="H54" s="35" t="s">
         <v>1374</v>
-      </c>
-      <c r="H54" s="35" t="s">
-        <v>1375</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40842,25 +40839,25 @@
         <v>54</v>
       </c>
       <c r="B55" s="28" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="C55" s="29" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D55" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E55" s="29" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="F55" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G55" s="34" t="s">
+        <v>1373</v>
+      </c>
+      <c r="H55" s="35" t="s">
         <v>1374</v>
-      </c>
-      <c r="H55" s="35" t="s">
-        <v>1375</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40868,25 +40865,25 @@
         <v>55</v>
       </c>
       <c r="B56" s="28" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="C56" s="29" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="D56" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E56" s="29" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="F56" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G56" s="34" t="s">
+        <v>1373</v>
+      </c>
+      <c r="H56" s="35" t="s">
         <v>1374</v>
-      </c>
-      <c r="H56" s="35" t="s">
-        <v>1375</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40894,25 +40891,25 @@
         <v>56</v>
       </c>
       <c r="B57" s="28" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C57" s="29" t="s">
         <v>1382</v>
-      </c>
-      <c r="C57" s="29" t="s">
-        <v>1383</v>
       </c>
       <c r="D57" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E57" s="29" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="F57" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G57" s="34" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H57" s="35" t="s">
         <v>1385</v>
-      </c>
-      <c r="H57" s="35" t="s">
-        <v>1386</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40920,25 +40917,25 @@
         <v>57</v>
       </c>
       <c r="B58" s="28" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="C58" s="29" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="D58" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E58" s="29" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="F58" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G58" s="34" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H58" s="35" t="s">
         <v>1385</v>
-      </c>
-      <c r="H58" s="35" t="s">
-        <v>1386</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40946,25 +40943,25 @@
         <v>58</v>
       </c>
       <c r="B59" s="28" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="C59" s="29" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="D59" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E59" s="29" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="F59" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G59" s="34" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H59" s="35" t="s">
         <v>1385</v>
-      </c>
-      <c r="H59" s="35" t="s">
-        <v>1386</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40972,25 +40969,25 @@
         <v>59</v>
       </c>
       <c r="B60" s="28" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="C60" s="29" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="D60" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E60" s="29" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="F60" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G60" s="34" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H60" s="35" t="s">
         <v>1385</v>
-      </c>
-      <c r="H60" s="35" t="s">
-        <v>1386</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40998,25 +40995,25 @@
         <v>60</v>
       </c>
       <c r="B61" s="28" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="C61" s="29" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="D61" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E61" s="29" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="F61" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G61" s="34" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H61" s="35" t="s">
         <v>1385</v>
-      </c>
-      <c r="H61" s="35" t="s">
-        <v>1386</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41024,25 +41021,25 @@
         <v>61</v>
       </c>
       <c r="B62" s="28" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="C62" s="29" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D62" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E62" s="29" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="F62" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G62" s="34" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H62" s="35" t="s">
         <v>1385</v>
-      </c>
-      <c r="H62" s="35" t="s">
-        <v>1386</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41050,25 +41047,25 @@
         <v>62</v>
       </c>
       <c r="B63" s="28" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="C63" s="29" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="D63" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E63" s="29" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="F63" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G63" s="34" t="s">
+        <v>1398</v>
+      </c>
+      <c r="H63" s="35" t="s">
         <v>1399</v>
-      </c>
-      <c r="H63" s="35" t="s">
-        <v>1400</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41076,25 +41073,25 @@
         <v>63</v>
       </c>
       <c r="B64" s="28" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="C64" s="29" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="D64" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E64" s="29" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="F64" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G64" s="34" t="s">
+        <v>1398</v>
+      </c>
+      <c r="H64" s="35" t="s">
         <v>1399</v>
-      </c>
-      <c r="H64" s="35" t="s">
-        <v>1400</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41102,25 +41099,25 @@
         <v>64</v>
       </c>
       <c r="B65" s="28" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="C65" s="29" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="D65" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E65" s="29" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="F65" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G65" s="34" t="s">
+        <v>1398</v>
+      </c>
+      <c r="H65" s="35" t="s">
         <v>1399</v>
-      </c>
-      <c r="H65" s="35" t="s">
-        <v>1400</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41128,25 +41125,25 @@
         <v>65</v>
       </c>
       <c r="B66" s="28" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="C66" s="29" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="D66" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E66" s="29" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="F66" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G66" s="34" t="s">
+        <v>1398</v>
+      </c>
+      <c r="H66" s="35" t="s">
         <v>1399</v>
-      </c>
-      <c r="H66" s="35" t="s">
-        <v>1400</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41154,25 +41151,25 @@
         <v>66</v>
       </c>
       <c r="B67" s="28" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C67" s="29" t="s">
         <v>1407</v>
-      </c>
-      <c r="C67" s="29" t="s">
-        <v>1408</v>
       </c>
       <c r="D67" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E67" s="29" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="F67" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G67" s="34" t="s">
+        <v>1409</v>
+      </c>
+      <c r="H67" s="35" t="s">
         <v>1410</v>
-      </c>
-      <c r="H67" s="35" t="s">
-        <v>1411</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41180,25 +41177,25 @@
         <v>67</v>
       </c>
       <c r="B68" s="28" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C68" s="29" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="D68" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E68" s="29" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="F68" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G68" s="34" t="s">
+        <v>1409</v>
+      </c>
+      <c r="H68" s="35" t="s">
         <v>1410</v>
-      </c>
-      <c r="H68" s="35" t="s">
-        <v>1411</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41206,25 +41203,25 @@
         <v>68</v>
       </c>
       <c r="B69" s="28" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C69" s="29" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="D69" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E69" s="29" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="F69" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G69" s="34" t="s">
+        <v>1409</v>
+      </c>
+      <c r="H69" s="35" t="s">
         <v>1410</v>
-      </c>
-      <c r="H69" s="35" t="s">
-        <v>1411</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41232,25 +41229,25 @@
         <v>69</v>
       </c>
       <c r="B70" s="28" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C70" s="29" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="D70" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E70" s="29" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="F70" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G70" s="34" t="s">
+        <v>1409</v>
+      </c>
+      <c r="H70" s="35" t="s">
         <v>1410</v>
-      </c>
-      <c r="H70" s="35" t="s">
-        <v>1411</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41258,25 +41255,25 @@
         <v>70</v>
       </c>
       <c r="B71" s="28" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C71" s="29" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="D71" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E71" s="29" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="F71" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G71" s="34" t="s">
+        <v>1409</v>
+      </c>
+      <c r="H71" s="35" t="s">
         <v>1410</v>
-      </c>
-      <c r="H71" s="35" t="s">
-        <v>1411</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41284,25 +41281,25 @@
         <v>71</v>
       </c>
       <c r="B72" s="28" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C72" s="29" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="D72" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E72" s="29" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="F72" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G72" s="34" t="s">
+        <v>1421</v>
+      </c>
+      <c r="H72" s="35" t="s">
         <v>1422</v>
-      </c>
-      <c r="H72" s="35" t="s">
-        <v>1423</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41310,25 +41307,25 @@
         <v>72</v>
       </c>
       <c r="B73" s="28" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C73" s="29" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="D73" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E73" s="29" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="F73" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G73" s="34" t="s">
+        <v>1421</v>
+      </c>
+      <c r="H73" s="35" t="s">
         <v>1422</v>
-      </c>
-      <c r="H73" s="35" t="s">
-        <v>1423</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41336,25 +41333,25 @@
         <v>73</v>
       </c>
       <c r="B74" s="28" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C74" s="29" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="D74" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E74" s="29" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="F74" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G74" s="34" t="s">
+        <v>1427</v>
+      </c>
+      <c r="H74" s="35" t="s">
         <v>1428</v>
-      </c>
-      <c r="H74" s="35" t="s">
-        <v>1429</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41362,25 +41359,25 @@
         <v>74</v>
       </c>
       <c r="B75" s="28" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C75" s="29" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="D75" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E75" s="29" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="F75" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G75" s="34" t="s">
+        <v>1427</v>
+      </c>
+      <c r="H75" s="35" t="s">
         <v>1428</v>
-      </c>
-      <c r="H75" s="35" t="s">
-        <v>1429</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41388,25 +41385,25 @@
         <v>75</v>
       </c>
       <c r="B76" s="28" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C76" s="29" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="D76" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E76" s="29" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="F76" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G76" s="34" t="s">
+        <v>1427</v>
+      </c>
+      <c r="H76" s="35" t="s">
         <v>1428</v>
-      </c>
-      <c r="H76" s="35" t="s">
-        <v>1429</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41414,25 +41411,25 @@
         <v>76</v>
       </c>
       <c r="B77" s="28" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C77" s="29" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="D77" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E77" s="29" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="F77" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G77" s="34" t="s">
+        <v>1435</v>
+      </c>
+      <c r="H77" s="35" t="s">
         <v>1436</v>
-      </c>
-      <c r="H77" s="35" t="s">
-        <v>1437</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41440,25 +41437,25 @@
         <v>77</v>
       </c>
       <c r="B78" s="28" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C78" s="29" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="D78" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E78" s="29" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="F78" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G78" s="34" t="s">
+        <v>1435</v>
+      </c>
+      <c r="H78" s="35" t="s">
         <v>1436</v>
-      </c>
-      <c r="H78" s="35" t="s">
-        <v>1437</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41466,25 +41463,25 @@
         <v>78</v>
       </c>
       <c r="B79" s="28" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C79" s="29" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="D79" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E79" s="29" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="F79" s="29" t="s">
         <v>25</v>
       </c>
       <c r="G79" s="34" t="s">
+        <v>1435</v>
+      </c>
+      <c r="H79" s="35" t="s">
         <v>1436</v>
-      </c>
-      <c r="H79" s="35" t="s">
-        <v>1437</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41492,25 +41489,25 @@
         <v>79</v>
       </c>
       <c r="B80" s="28" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C80" s="29" t="s">
         <v>1442</v>
-      </c>
-      <c r="C80" s="29" t="s">
-        <v>1443</v>
       </c>
       <c r="D80" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E80" s="29" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="F80" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G80" s="34" t="s">
+        <v>1444</v>
+      </c>
+      <c r="H80" s="35" t="s">
         <v>1445</v>
-      </c>
-      <c r="H80" s="35" t="s">
-        <v>1446</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41518,25 +41515,25 @@
         <v>80</v>
       </c>
       <c r="B81" s="28" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="C81" s="29" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="D81" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E81" s="29" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="F81" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G81" s="34" t="s">
+        <v>1444</v>
+      </c>
+      <c r="H81" s="35" t="s">
         <v>1445</v>
-      </c>
-      <c r="H81" s="35" t="s">
-        <v>1446</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41544,25 +41541,25 @@
         <v>81</v>
       </c>
       <c r="B82" s="28" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="C82" s="29" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="D82" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E82" s="29" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="F82" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G82" s="34" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H82" s="35" t="s">
         <v>1451</v>
-      </c>
-      <c r="H82" s="35" t="s">
-        <v>1452</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41570,25 +41567,25 @@
         <v>82</v>
       </c>
       <c r="B83" s="28" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="C83" s="29" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="D83" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E83" s="29" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="F83" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G83" s="34" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H83" s="35" t="s">
         <v>1451</v>
-      </c>
-      <c r="H83" s="35" t="s">
-        <v>1452</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41596,25 +41593,25 @@
         <v>83</v>
       </c>
       <c r="B84" s="28" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="C84" s="29" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="D84" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E84" s="29" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="F84" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G84" s="34" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H84" s="35" t="s">
         <v>1451</v>
-      </c>
-      <c r="H84" s="35" t="s">
-        <v>1452</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41622,25 +41619,25 @@
         <v>84</v>
       </c>
       <c r="B85" s="28" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="C85" s="29" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="D85" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E85" s="29" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="F85" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G85" s="34" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H85" s="35" t="s">
         <v>1451</v>
-      </c>
-      <c r="H85" s="35" t="s">
-        <v>1452</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41648,25 +41645,25 @@
         <v>85</v>
       </c>
       <c r="B86" s="28" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="C86" s="29" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="D86" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E86" s="29" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="F86" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G86" s="34" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H86" s="35" t="s">
         <v>1451</v>
-      </c>
-      <c r="H86" s="35" t="s">
-        <v>1452</v>
       </c>
     </row>
   </sheetData>
@@ -41678,9 +41675,9 @@
     <hyperlink ref="H3" r:id="rId4" display="https://www.mois.go.kr/chd/sub/a06/road/screen.do"/>
     <hyperlink ref="G4" r:id="rId5" display="어린이 안전 배움터 - 도로·교통(어린이보호구역 교통안전수칙)"/>
     <hyperlink ref="H4" r:id="rId6" display="https://www.mois.go.kr/chd/sub/a06/road/screen.do"/>
-    <hyperlink ref="G5" r:id="rId7" display="어린이 생활안전 &gt; 교통안전 &gt; 어린이 보행안전 &gt; 어린이 보행사고 예방을 위한 안전수칙 (도로교통법 제10조제2항)"/>
+    <hyperlink ref="G5" r:id="rId7" display="찾기쉬운 생활법령정보 - 어린이 보행사고 예방을 위한 안전수칙(도로교통법 제10조제2항)"/>
     <hyperlink ref="H5" r:id="rId8" display="https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=1"/>
-    <hyperlink ref="G6" r:id="rId9" display="안전 배움터 &gt; 도로·교통 &gt; 어린이보호구역 교통안전수칙"/>
+    <hyperlink ref="G6" r:id="rId9" display="어린이 안전 배움터 - 도로·교통(어린이보호구역 교통안전수칙)"/>
     <hyperlink ref="H6" r:id="rId10" display="https://www.mois.go.kr/chd/sub/a06/road/screen.do"/>
     <hyperlink ref="G7" r:id="rId11" display="어린이 안전 배움터 - 도로·교통(어린이보호구역 교통안전수칙)"/>
     <hyperlink ref="H7" r:id="rId12" display="https://www.mois.go.kr/chd/sub/a06/road/screen.do"/>
@@ -41904,25 +41901,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="28" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C2" s="29" t="s">
         <v>1461</v>
-      </c>
-      <c r="C2" s="29" t="s">
-        <v>1462</v>
       </c>
       <c r="D2" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E2" s="29" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="F2" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G2" s="34" t="s">
+        <v>1463</v>
+      </c>
+      <c r="H2" s="35" t="s">
         <v>1464</v>
-      </c>
-      <c r="H2" s="35" t="s">
-        <v>1465</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41930,25 +41927,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="D3" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="F3" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G3" s="34" t="s">
+        <v>1463</v>
+      </c>
+      <c r="H3" s="35" t="s">
         <v>1464</v>
-      </c>
-      <c r="H3" s="35" t="s">
-        <v>1465</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41956,25 +41953,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="D4" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="F4" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G4" s="34" t="s">
+        <v>1469</v>
+      </c>
+      <c r="H4" s="35" t="s">
         <v>1470</v>
-      </c>
-      <c r="H4" s="35" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41982,25 +41979,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="D5" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="F5" s="29" t="s">
         <v>27</v>
       </c>
       <c r="G5" s="37" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H5" s="35" t="s">
         <v>1474</v>
-      </c>
-      <c r="H5" s="35" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42008,25 +42005,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="D6" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="F6" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G6" s="34" t="s">
+        <v>1463</v>
+      </c>
+      <c r="H6" s="35" t="s">
         <v>1464</v>
-      </c>
-      <c r="H6" s="35" t="s">
-        <v>1465</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42034,25 +42031,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="D7" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="F7" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G7" s="34" t="s">
+        <v>1463</v>
+      </c>
+      <c r="H7" s="35" t="s">
         <v>1464</v>
-      </c>
-      <c r="H7" s="35" t="s">
-        <v>1465</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42060,25 +42057,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="D8" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="F8" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G8" s="34" t="s">
+        <v>1481</v>
+      </c>
+      <c r="H8" s="35" t="s">
         <v>1482</v>
-      </c>
-      <c r="H8" s="35" t="s">
-        <v>1483</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42086,25 +42083,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="D9" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="F9" s="29" t="s">
         <v>27</v>
       </c>
       <c r="G9" s="37" t="s">
+        <v>1485</v>
+      </c>
+      <c r="H9" s="35" t="s">
         <v>1486</v>
-      </c>
-      <c r="H9" s="35" t="s">
-        <v>1487</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42112,25 +42109,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="28" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C10" s="29" t="s">
         <v>1488</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>1489</v>
       </c>
       <c r="D10" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="F10" s="29" t="s">
         <v>27</v>
       </c>
       <c r="G10" s="37" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H10" s="35" t="s">
         <v>1474</v>
-      </c>
-      <c r="H10" s="35" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42138,25 +42135,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="D11" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="F11" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G11" s="34" t="s">
+        <v>1469</v>
+      </c>
+      <c r="H11" s="35" t="s">
         <v>1470</v>
-      </c>
-      <c r="H11" s="35" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42164,25 +42161,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="D12" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E12" s="29" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="F12" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G12" s="34" t="s">
+        <v>1469</v>
+      </c>
+      <c r="H12" s="35" t="s">
         <v>1470</v>
-      </c>
-      <c r="H12" s="35" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42190,25 +42187,25 @@
         <v>12</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="D13" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E13" s="29" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="F13" s="29" t="s">
         <v>27</v>
       </c>
       <c r="G13" s="37" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H13" s="35" t="s">
         <v>1474</v>
-      </c>
-      <c r="H13" s="35" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42216,25 +42213,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="D14" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="F14" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G14" s="34" t="s">
+        <v>1469</v>
+      </c>
+      <c r="H14" s="35" t="s">
         <v>1470</v>
-      </c>
-      <c r="H14" s="35" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42242,25 +42239,25 @@
         <v>14</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="D15" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E15" s="29" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="F15" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G15" s="34" t="s">
+        <v>1500</v>
+      </c>
+      <c r="H15" s="35" t="s">
         <v>1501</v>
-      </c>
-      <c r="H15" s="35" t="s">
-        <v>1502</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42268,25 +42265,25 @@
         <v>15</v>
       </c>
       <c r="B16" s="28" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C16" s="29" t="s">
         <v>1503</v>
-      </c>
-      <c r="C16" s="29" t="s">
-        <v>1504</v>
       </c>
       <c r="D16" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="F16" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G16" s="34" t="s">
+        <v>1469</v>
+      </c>
+      <c r="H16" s="35" t="s">
         <v>1470</v>
-      </c>
-      <c r="H16" s="35" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42294,25 +42291,25 @@
         <v>16</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="D17" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="F17" s="29" t="s">
         <v>27</v>
       </c>
       <c r="G17" s="37" t="s">
+        <v>1485</v>
+      </c>
+      <c r="H17" s="35" t="s">
         <v>1486</v>
-      </c>
-      <c r="H17" s="35" t="s">
-        <v>1487</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42320,25 +42317,25 @@
         <v>17</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="D18" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="F18" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G18" s="34" t="s">
+        <v>1469</v>
+      </c>
+      <c r="H18" s="35" t="s">
         <v>1470</v>
-      </c>
-      <c r="H18" s="35" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42346,25 +42343,25 @@
         <v>18</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="D19" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E19" s="29" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="F19" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G19" s="34" t="s">
+        <v>1469</v>
+      </c>
+      <c r="H19" s="35" t="s">
         <v>1470</v>
-      </c>
-      <c r="H19" s="35" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42372,25 +42369,25 @@
         <v>19</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="D20" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="F20" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G20" s="34" t="s">
+        <v>1463</v>
+      </c>
+      <c r="H20" s="35" t="s">
         <v>1464</v>
-      </c>
-      <c r="H20" s="35" t="s">
-        <v>1465</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42398,25 +42395,25 @@
         <v>20</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="D21" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E21" s="29" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="F21" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G21" s="34" t="s">
+        <v>1515</v>
+      </c>
+      <c r="H21" s="35" t="s">
         <v>1516</v>
-      </c>
-      <c r="H21" s="35" t="s">
-        <v>1517</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42424,25 +42421,25 @@
         <v>21</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="D22" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E22" s="29" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="F22" s="29" t="s">
         <v>27</v>
       </c>
       <c r="G22" s="37" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H22" s="35" t="s">
         <v>1474</v>
-      </c>
-      <c r="H22" s="35" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42450,25 +42447,25 @@
         <v>22</v>
       </c>
       <c r="B23" s="28" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C23" s="29" t="s">
         <v>1520</v>
-      </c>
-      <c r="C23" s="29" t="s">
-        <v>1521</v>
       </c>
       <c r="D23" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E23" s="29" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="F23" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G23" s="34" t="s">
+        <v>1469</v>
+      </c>
+      <c r="H23" s="35" t="s">
         <v>1470</v>
-      </c>
-      <c r="H23" s="35" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42476,25 +42473,25 @@
         <v>23</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="D24" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E24" s="29" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="F24" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G24" s="34" t="s">
+        <v>1469</v>
+      </c>
+      <c r="H24" s="35" t="s">
         <v>1470</v>
-      </c>
-      <c r="H24" s="35" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42502,25 +42499,25 @@
         <v>24</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="D25" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E25" s="29" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="F25" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G25" s="34" t="s">
+        <v>1463</v>
+      </c>
+      <c r="H25" s="35" t="s">
         <v>1464</v>
-      </c>
-      <c r="H25" s="35" t="s">
-        <v>1465</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42528,25 +42525,25 @@
         <v>25</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="D26" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E26" s="29" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="F26" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G26" s="34" t="s">
+        <v>1469</v>
+      </c>
+      <c r="H26" s="35" t="s">
         <v>1470</v>
-      </c>
-      <c r="H26" s="35" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42554,25 +42551,25 @@
         <v>26</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="D27" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E27" s="29" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="F27" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G27" s="34" t="s">
+        <v>1469</v>
+      </c>
+      <c r="H27" s="35" t="s">
         <v>1470</v>
-      </c>
-      <c r="H27" s="35" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42580,25 +42577,25 @@
         <v>27</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="D28" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E28" s="29" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="F28" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G28" s="34" t="s">
+        <v>1469</v>
+      </c>
+      <c r="H28" s="35" t="s">
         <v>1470</v>
-      </c>
-      <c r="H28" s="35" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42606,25 +42603,25 @@
         <v>28</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="D29" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E29" s="29" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="F29" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G29" s="34" t="s">
+        <v>1469</v>
+      </c>
+      <c r="H29" s="35" t="s">
         <v>1470</v>
-      </c>
-      <c r="H29" s="35" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42632,25 +42629,25 @@
         <v>29</v>
       </c>
       <c r="B30" s="28" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C30" s="29" t="s">
         <v>1535</v>
-      </c>
-      <c r="C30" s="29" t="s">
-        <v>1536</v>
       </c>
       <c r="D30" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E30" s="29" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="F30" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G30" s="34" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H30" s="35" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42658,25 +42655,25 @@
         <v>30</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="D31" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E31" s="29" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="F31" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G31" s="34" t="s">
+        <v>1469</v>
+      </c>
+      <c r="H31" s="35" t="s">
         <v>1470</v>
-      </c>
-      <c r="H31" s="35" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42684,25 +42681,25 @@
         <v>31</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="D32" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E32" s="29" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="F32" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G32" s="34" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H32" s="35" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42710,25 +42707,25 @@
         <v>32</v>
       </c>
       <c r="B33" s="28" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C33" s="29" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="D33" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E33" s="29" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="F33" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G33" s="34" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="H33" s="35" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42736,25 +42733,25 @@
         <v>33</v>
       </c>
       <c r="B34" s="28" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C34" s="39" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="D34" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E34" s="29" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="F34" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G34" s="34" t="s">
+        <v>1469</v>
+      </c>
+      <c r="H34" s="35" t="s">
         <v>1470</v>
-      </c>
-      <c r="H34" s="35" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42762,25 +42759,25 @@
         <v>34</v>
       </c>
       <c r="B35" s="28" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="D35" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E35" s="29" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="F35" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G35" s="34" t="s">
+        <v>1549</v>
+      </c>
+      <c r="H35" s="35" t="s">
         <v>1550</v>
-      </c>
-      <c r="H35" s="35" t="s">
-        <v>1551</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42788,25 +42785,25 @@
         <v>35</v>
       </c>
       <c r="B36" s="28" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C36" s="29" t="s">
         <v>1552</v>
-      </c>
-      <c r="C36" s="29" t="s">
-        <v>1553</v>
       </c>
       <c r="D36" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="F36" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G36" s="34" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H36" s="35" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42814,25 +42811,25 @@
         <v>36</v>
       </c>
       <c r="B37" s="28" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="D37" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E37" s="29" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="F37" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G37" s="34" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H37" s="35" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42840,25 +42837,25 @@
         <v>37</v>
       </c>
       <c r="B38" s="28" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="D38" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E38" s="29" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="F38" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G38" s="34" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H38" s="35" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42866,25 +42863,25 @@
         <v>38</v>
       </c>
       <c r="B39" s="28" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="D39" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="F39" s="29" t="s">
         <v>37</v>
       </c>
       <c r="G39" s="37" t="s">
+        <v>1561</v>
+      </c>
+      <c r="H39" s="35" t="s">
         <v>1562</v>
-      </c>
-      <c r="H39" s="35" t="s">
-        <v>1563</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42892,25 +42889,25 @@
         <v>39</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="D40" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="F40" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G40" s="34" t="s">
+        <v>1469</v>
+      </c>
+      <c r="H40" s="35" t="s">
         <v>1470</v>
-      </c>
-      <c r="H40" s="35" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42918,25 +42915,25 @@
         <v>40</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="D41" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E41" s="29" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="F41" s="29" t="s">
         <v>27</v>
       </c>
       <c r="G41" s="37" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H41" s="35" t="s">
         <v>1474</v>
-      </c>
-      <c r="H41" s="35" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42944,25 +42941,25 @@
         <v>41</v>
       </c>
       <c r="B42" s="28" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="D42" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E42" s="29" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="F42" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G42" s="34" t="s">
+        <v>1569</v>
+      </c>
+      <c r="H42" s="35" t="s">
         <v>1570</v>
-      </c>
-      <c r="H42" s="35" t="s">
-        <v>1571</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42970,25 +42967,25 @@
         <v>42</v>
       </c>
       <c r="B43" s="28" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="D43" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E43" s="29" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="F43" s="29" t="s">
         <v>37</v>
       </c>
       <c r="G43" s="37" t="s">
+        <v>1561</v>
+      </c>
+      <c r="H43" s="35" t="s">
         <v>1562</v>
-      </c>
-      <c r="H43" s="35" t="s">
-        <v>1563</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42996,25 +42993,25 @@
         <v>43</v>
       </c>
       <c r="B44" s="28" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="D44" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E44" s="29" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="F44" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G44" s="34" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H44" s="35" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43022,25 +43019,25 @@
         <v>44</v>
       </c>
       <c r="B45" s="28" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="C45" s="29" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="D45" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E45" s="29" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="F45" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G45" s="34" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H45" s="35" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43048,25 +43045,25 @@
         <v>45</v>
       </c>
       <c r="B46" s="28" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="C46" s="29" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="D46" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E46" s="29" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="F46" s="29" t="s">
         <v>27</v>
       </c>
       <c r="G46" s="34" t="s">
+        <v>1580</v>
+      </c>
+      <c r="H46" s="35" t="s">
         <v>1581</v>
-      </c>
-      <c r="H46" s="35" t="s">
-        <v>1582</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43074,25 +43071,25 @@
         <v>46</v>
       </c>
       <c r="B47" s="28" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="C47" s="29" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="D47" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E47" s="29" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="F47" s="29" t="s">
         <v>37</v>
       </c>
       <c r="G47" s="37" t="s">
+        <v>1561</v>
+      </c>
+      <c r="H47" s="35" t="s">
         <v>1562</v>
-      </c>
-      <c r="H47" s="35" t="s">
-        <v>1563</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43100,25 +43097,25 @@
         <v>47</v>
       </c>
       <c r="B48" s="28" t="s">
+        <v>1584</v>
+      </c>
+      <c r="C48" s="29" t="s">
         <v>1585</v>
-      </c>
-      <c r="C48" s="29" t="s">
-        <v>1586</v>
       </c>
       <c r="D48" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E48" s="29" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="F48" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G48" s="34" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H48" s="35" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43126,25 +43123,25 @@
         <v>48</v>
       </c>
       <c r="B49" s="28" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="C49" s="29" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="D49" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E49" s="29" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="F49" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G49" s="34" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H49" s="35" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43152,25 +43149,25 @@
         <v>49</v>
       </c>
       <c r="B50" s="28" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="C50" s="29" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="D50" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E50" s="29" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="F50" s="29" t="s">
         <v>27</v>
       </c>
       <c r="G50" s="37" t="s">
+        <v>1485</v>
+      </c>
+      <c r="H50" s="35" t="s">
         <v>1486</v>
-      </c>
-      <c r="H50" s="35" t="s">
-        <v>1487</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43178,25 +43175,25 @@
         <v>50</v>
       </c>
       <c r="B51" s="28" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="C51" s="29" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="D51" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E51" s="29" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="F51" s="29" t="s">
         <v>27</v>
       </c>
       <c r="G51" s="37" t="s">
+        <v>1485</v>
+      </c>
+      <c r="H51" s="35" t="s">
         <v>1486</v>
-      </c>
-      <c r="H51" s="35" t="s">
-        <v>1487</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43204,25 +43201,25 @@
         <v>51</v>
       </c>
       <c r="B52" s="28" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="C52" s="29" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="D52" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E52" s="29" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="F52" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G52" s="34" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H52" s="35" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43230,25 +43227,25 @@
         <v>52</v>
       </c>
       <c r="B53" s="28" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="C53" s="29" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="D53" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E53" s="29" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="F53" s="29" t="s">
         <v>27</v>
       </c>
       <c r="G53" s="37" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H53" s="35" t="s">
         <v>1474</v>
-      </c>
-      <c r="H53" s="35" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43256,25 +43253,25 @@
         <v>53</v>
       </c>
       <c r="B54" s="28" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="C54" s="29" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="D54" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E54" s="29" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F54" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G54" s="34" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H54" s="35" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43282,25 +43279,25 @@
         <v>54</v>
       </c>
       <c r="B55" s="28" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C55" s="29" t="s">
         <v>1603</v>
-      </c>
-      <c r="C55" s="29" t="s">
-        <v>1604</v>
       </c>
       <c r="D55" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E55" s="29" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="F55" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G55" s="34" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H55" s="35" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43308,25 +43305,25 @@
         <v>55</v>
       </c>
       <c r="B56" s="28" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="C56" s="39" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="D56" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E56" s="29" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="F56" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G56" s="34" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H56" s="35" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43334,25 +43331,25 @@
         <v>56</v>
       </c>
       <c r="B57" s="28" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="C57" s="29" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="D57" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E57" s="29" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="F57" s="29" t="s">
         <v>38</v>
       </c>
       <c r="G57" s="34" t="s">
+        <v>1610</v>
+      </c>
+      <c r="H57" s="35" t="s">
         <v>1611</v>
-      </c>
-      <c r="H57" s="35" t="s">
-        <v>1612</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43360,25 +43357,25 @@
         <v>57</v>
       </c>
       <c r="B58" s="28" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="C58" s="29" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="D58" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E58" s="29" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="F58" s="29" t="s">
         <v>38</v>
       </c>
       <c r="G58" s="34" t="s">
+        <v>1610</v>
+      </c>
+      <c r="H58" s="35" t="s">
         <v>1611</v>
-      </c>
-      <c r="H58" s="35" t="s">
-        <v>1612</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43386,25 +43383,25 @@
         <v>58</v>
       </c>
       <c r="B59" s="28" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="C59" s="29" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="D59" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E59" s="29" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="F59" s="29" t="s">
         <v>38</v>
       </c>
       <c r="G59" s="34" t="s">
+        <v>1610</v>
+      </c>
+      <c r="H59" s="35" t="s">
         <v>1611</v>
-      </c>
-      <c r="H59" s="35" t="s">
-        <v>1612</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43412,25 +43409,25 @@
         <v>59</v>
       </c>
       <c r="B60" s="28" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="C60" s="29" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="D60" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E60" s="29" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="F60" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G60" s="34" t="s">
+        <v>1469</v>
+      </c>
+      <c r="H60" s="35" t="s">
         <v>1470</v>
-      </c>
-      <c r="H60" s="35" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43438,25 +43435,25 @@
         <v>60</v>
       </c>
       <c r="B61" s="28" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="C61" s="29" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="D61" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E61" s="29" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="F61" s="29" t="s">
         <v>39</v>
       </c>
       <c r="G61" s="34" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H61" s="35" t="s">
         <v>1621</v>
-      </c>
-      <c r="H61" s="35" t="s">
-        <v>1622</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43464,25 +43461,25 @@
         <v>61</v>
       </c>
       <c r="B62" s="28" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="C62" s="29" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="D62" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E62" s="29" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="F62" s="29" t="s">
         <v>27</v>
       </c>
       <c r="G62" s="37" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H62" s="35" t="s">
         <v>1474</v>
-      </c>
-      <c r="H62" s="35" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43490,25 +43487,25 @@
         <v>62</v>
       </c>
       <c r="B63" s="28" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="C63" s="29" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="D63" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E63" s="29" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="F63" s="29" t="s">
         <v>27</v>
       </c>
       <c r="G63" s="37" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H63" s="35" t="s">
         <v>1474</v>
-      </c>
-      <c r="H63" s="35" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43516,25 +43513,25 @@
         <v>63</v>
       </c>
       <c r="B64" s="28" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="C64" s="29" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="D64" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E64" s="29" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="F64" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G64" s="34" t="s">
+        <v>1628</v>
+      </c>
+      <c r="H64" s="35" t="s">
         <v>1629</v>
-      </c>
-      <c r="H64" s="35" t="s">
-        <v>1630</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43542,25 +43539,25 @@
         <v>64</v>
       </c>
       <c r="B65" s="28" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="C65" s="29" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="D65" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E65" s="29" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="F65" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G65" s="34" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H65" s="35" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43568,25 +43565,25 @@
         <v>65</v>
       </c>
       <c r="B66" s="28" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="C66" s="29" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="D66" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E66" s="29" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="F66" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G66" s="34" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H66" s="35" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43594,25 +43591,25 @@
         <v>66</v>
       </c>
       <c r="B67" s="28" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C67" s="29" t="s">
         <v>1635</v>
-      </c>
-      <c r="C67" s="29" t="s">
-        <v>1636</v>
       </c>
       <c r="D67" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E67" s="29" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="F67" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G67" s="34" t="s">
+        <v>1569</v>
+      </c>
+      <c r="H67" s="35" t="s">
         <v>1570</v>
-      </c>
-      <c r="H67" s="35" t="s">
-        <v>1571</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43620,25 +43617,25 @@
         <v>67</v>
       </c>
       <c r="B68" s="28" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="C68" s="29" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="D68" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E68" s="29" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="F68" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G68" s="34" t="s">
+        <v>1639</v>
+      </c>
+      <c r="H68" s="35" t="s">
         <v>1640</v>
-      </c>
-      <c r="H68" s="35" t="s">
-        <v>1641</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43646,25 +43643,25 @@
         <v>68</v>
       </c>
       <c r="B69" s="28" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="C69" s="29" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="D69" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E69" s="29" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="F69" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G69" s="34" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="H69" s="35" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43672,25 +43669,25 @@
         <v>69</v>
       </c>
       <c r="B70" s="28" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="C70" s="29" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="D70" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E70" s="29" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="F70" s="29" t="s">
         <v>27</v>
       </c>
       <c r="G70" s="34" t="s">
+        <v>1646</v>
+      </c>
+      <c r="H70" s="35" t="s">
         <v>1647</v>
-      </c>
-      <c r="H70" s="35" t="s">
-        <v>1648</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43698,25 +43695,25 @@
         <v>70</v>
       </c>
       <c r="B71" s="28" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="C71" s="29" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="D71" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E71" s="29" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="F71" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G71" s="34" t="s">
+        <v>1569</v>
+      </c>
+      <c r="H71" s="35" t="s">
         <v>1570</v>
-      </c>
-      <c r="H71" s="35" t="s">
-        <v>1571</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43724,25 +43721,25 @@
         <v>71</v>
       </c>
       <c r="B72" s="28" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="C72" s="29" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="D72" s="36" t="s">
         <v>1034</v>
       </c>
       <c r="E72" s="29" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="F72" s="29" t="s">
         <v>24</v>
       </c>
       <c r="G72" s="34" t="s">
+        <v>1569</v>
+      </c>
+      <c r="H72" s="35" t="s">
         <v>1570</v>
-      </c>
-      <c r="H72" s="35" t="s">
-        <v>1571</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43750,25 +43747,25 @@
         <v>72</v>
       </c>
       <c r="B73" s="28" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="C73" s="29" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="D73" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="E73" s="29" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="F73" s="29" t="s">
         <v>27</v>
       </c>
       <c r="G73" s="34" t="s">
+        <v>1654</v>
+      </c>
+      <c r="H73" s="35" t="s">
         <v>1655</v>
-      </c>
-      <c r="H73" s="35" t="s">
-        <v>1656</v>
       </c>
     </row>
   </sheetData>
@@ -43953,7 +43950,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43961,15 +43958,15 @@
         <v>1021</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="42" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B5" s="43" t="s">
         <v>1659</v>
-      </c>
-      <c r="B5" s="43" t="s">
-        <v>1660</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43977,7 +43974,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43986,34 +43983,34 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="42" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B8" s="45" t="s">
         <v>1662</v>
-      </c>
-      <c r="B8" s="45" t="s">
-        <v>1663</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="42"/>
       <c r="B9" s="45" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="42"/>
       <c r="B10" s="45" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="42"/>
       <c r="B11" s="43" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="42"/>
       <c r="B12" s="43" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44022,10 +44019,10 @@
     </row>
     <row r="14" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="42" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B14" s="43" t="s">
         <v>1668</v>
-      </c>
-      <c r="B14" s="43" t="s">
-        <v>1669</v>
       </c>
     </row>
   </sheetData>

--- a/quiz/간단교육_퀴즈_문항집.xlsx
+++ b/quiz/간단교육_퀴즈_문항집.xlsx
@@ -3602,7 +3602,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">음식을 매우 맛있게 순식간에 다 먹어 치움을 비유하는 말</t>
+      <t xml:space="preserve">음식을 눈 깜짝할 사이에 매우 빨리 먹어 치움을 이르는 말</t>
     </r>
     <r>
       <rPr>
@@ -4358,7 +4358,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">눈앞에 놓인 가장 기초적이고 쉬운 글자나 이치도 모를 만큼 무식함을 뜻함</t>
+      <t xml:space="preserve">아주 쉽고 기본적인 것도 알지 못함을 이르는 말</t>
     </r>
     <r>
       <rPr>
@@ -5386,7 +5386,7 @@
     <t xml:space="preserve">수불석권</t>
   </si>
   <si>
-    <t xml:space="preserve">手不釋卷</t>
+    <t xml:space="preserve">手不釋卷</t>
   </si>
   <si>
     <t xml:space="preserve">권</t>
@@ -5563,7 +5563,7 @@
     <t xml:space="preserve">불치하문</t>
   </si>
   <si>
-    <t xml:space="preserve">不恥下問</t>
+    <t xml:space="preserve">不恥下問</t>
   </si>
   <si>
     <r>
@@ -6086,7 +6086,7 @@
     <t xml:space="preserve">자강불식</t>
   </si>
   <si>
-    <t xml:space="preserve">自强不息</t>
+    <t xml:space="preserve">自强不息</t>
   </si>
   <si>
     <r>
@@ -6255,7 +6255,7 @@
     <t xml:space="preserve">백절불굴</t>
   </si>
   <si>
-    <t xml:space="preserve">百折不屈</t>
+    <t xml:space="preserve">百折不屈</t>
   </si>
   <si>
     <r>
@@ -6574,7 +6574,7 @@
     <t xml:space="preserve">동고동락</t>
   </si>
   <si>
-    <t xml:space="preserve">同苦同樂</t>
+    <t xml:space="preserve">同苦同樂</t>
   </si>
   <si>
     <t xml:space="preserve">락</t>
@@ -6721,7 +6721,7 @@
     <t xml:space="preserve">금란지교</t>
   </si>
   <si>
-    <t xml:space="preserve">金蘭之交</t>
+    <t xml:space="preserve">金蘭之交</t>
   </si>
   <si>
     <r>
@@ -6808,7 +6808,7 @@
     <t xml:space="preserve">과유불급</t>
   </si>
   <si>
-    <t xml:space="preserve">過猶不及</t>
+    <t xml:space="preserve">過猶不及</t>
   </si>
   <si>
     <t xml:space="preserve">과</t>
@@ -7105,7 +7105,7 @@
     <t xml:space="preserve">안빈낙도</t>
   </si>
   <si>
-    <t xml:space="preserve">安貧樂道</t>
+    <t xml:space="preserve">安貧樂道</t>
   </si>
   <si>
     <r>
@@ -7395,7 +7395,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">인생의 길흉화복은 변화가 무쌍하여 예측하기 어려우니 일희일비하지 말아야 함</t>
+      <t xml:space="preserve">변방 노인의 말 이야기에서 나온 말로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">좋은 일과 나쁜 일은 번갈아 찾아오니 눈앞의 일에 너무 기뻐하거나 슬퍼하지 말아야 함</t>
     </r>
     <r>
       <rPr>
@@ -7458,7 +7477,7 @@
     <t xml:space="preserve">일거양득</t>
   </si>
   <si>
-    <t xml:space="preserve">一擧兩得</t>
+    <t xml:space="preserve">一擧兩得</t>
   </si>
   <si>
     <r>
@@ -7730,7 +7749,7 @@
     <t xml:space="preserve">진퇴양난</t>
   </si>
   <si>
-    <t xml:space="preserve">進退兩難</t>
+    <t xml:space="preserve">進退兩難</t>
   </si>
   <si>
     <r>
@@ -7767,7 +7786,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">사방에서 들려오는 적의 노래처럼</t>
+      <t xml:space="preserve">사방에서 고향인 초나라 노래가 들려왔다는 뜻으로</t>
     </r>
     <r>
       <rPr>
@@ -7786,7 +7805,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">사방이 적으로 둘러싸여 고립된 상태</t>
+      <t xml:space="preserve">아무 도움도 받을 수 없는 외롭고 어려운 처지</t>
     </r>
     <r>
       <rPr>
@@ -7965,7 +7984,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">간사한 꾀로 남을 속이고 농락함</t>
+      <t xml:space="preserve">눈앞의 차이만 보고 속거나 얕은 꾀로 남을 속임</t>
     </r>
     <r>
       <rPr>
@@ -8044,7 +8063,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">양 머리를 걸어놓고 개고기를 팔듯</t>
+      <t xml:space="preserve">양 머리를 걸어놓고 다른 고기를 판다는 뜻으로</t>
     </r>
     <r>
       <rPr>
@@ -8063,7 +8082,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">겉은 번지르르하나 속은 엉터리임</t>
+      <t xml:space="preserve">겉만 그럴듯하고 속은 다름</t>
     </r>
     <r>
       <rPr>
@@ -8093,7 +8112,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">겉과 속이 서로 달라서 마음이 음흉하고 솔직하지 못함</t>
+      <t xml:space="preserve">겉과 속이 달라 솔직하지 못함</t>
     </r>
     <r>
       <rPr>
@@ -8186,7 +8205,7 @@
     <t xml:space="preserve">사상누각</t>
   </si>
   <si>
-    <t xml:space="preserve">砂上樓閣</t>
+    <t xml:space="preserve">砂上樓閣</t>
   </si>
   <si>
     <r>
@@ -8213,7 +8232,7 @@
     <t xml:space="preserve">용두사미</t>
   </si>
   <si>
-    <t xml:space="preserve">龍頭蛇尾</t>
+    <t xml:space="preserve">龍頭蛇尾</t>
   </si>
   <si>
     <t xml:space="preserve">용</t>
@@ -8332,7 +8351,34 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">눈 아래에 사람이 없다는 뜻으로</t>
+      <t xml:space="preserve">잘난 척하며 다른 사람을 함부로 얕봄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">마이동풍</t>
+  </si>
+  <si>
+    <t xml:space="preserve">馬耳東風</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">말의 귀에 부는 봄바람처럼</t>
     </r>
     <r>
       <rPr>
@@ -8351,34 +8397,34 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">방자하고 교만하여 남을 얕봄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">마이동풍</t>
-  </si>
-  <si>
-    <t xml:space="preserve">馬耳東風</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">말의 귀에 부는 봄바람처럼</t>
+      <t xml:space="preserve">남의 충고나 의견을 귀담아듣지 않고 흘려버림</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">수수방관</t>
+  </si>
+  <si>
+    <t xml:space="preserve">袖手傍觀</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">팔짱을 끼고 곁에서 바라만 본다는 뜻으로</t>
     </r>
     <r>
       <rPr>
@@ -8397,34 +8443,40 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">남의 충고나 의견을 귀담아듣지 않고 흘려버림</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">수수방관</t>
-  </si>
-  <si>
-    <t xml:space="preserve">袖手傍觀</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">팔짱을 끼고 곁에서 바라만 본다는 뜻으로</t>
+      <t xml:space="preserve">마땅히 도울 일에 간섭하지 않고 방치함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">당랑거철</t>
+  </si>
+  <si>
+    <t xml:space="preserve">螳螂拒轍</t>
+  </si>
+  <si>
+    <t xml:space="preserve">당</t>
+  </si>
+  <si>
+    <t xml:space="preserve">철</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사마귀가 수레를 막아서듯</t>
     </r>
     <r>
       <rPr>
@@ -8443,40 +8495,64 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">마땅히 도울 일에 간섭하지 않고 방치함</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">당랑거철</t>
-  </si>
-  <si>
-    <t xml:space="preserve">螳螂拒轍</t>
-  </si>
-  <si>
-    <t xml:space="preserve">당</t>
-  </si>
-  <si>
-    <t xml:space="preserve">철</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사마귀가 수레를 막아서듯</t>
+      <t xml:space="preserve">제 힘도 모르고 무리하게 덤빔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">정저지와</t>
+  </si>
+  <si>
+    <t xml:space="preserve">井底之蛙</t>
+  </si>
+  <si>
+    <t xml:space="preserve">와</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">우물 안 개구리처럼 세상이 넓은 줄 모르고 아는 것이 좁음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">오비이락</t>
+  </si>
+  <si>
+    <t xml:space="preserve">烏飛梨落</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">까마귀 날자 배 떨어진다는 뜻으로</t>
     </r>
     <r>
       <rPr>
@@ -8495,64 +8571,37 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">제 힘도 모르고 무리하게 덤빔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">정저지와</t>
-  </si>
-  <si>
-    <t xml:space="preserve">井底之蛙</t>
-  </si>
-  <si>
-    <t xml:space="preserve">와</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">우물 안 개구리처럼 세상 넓은 줄 모르고 견문이 좁음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">오비이락</t>
-  </si>
-  <si>
-    <t xml:space="preserve">烏飛梨落</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">까마귀 날자 배 떨어진다는 뜻으로</t>
+      <t xml:space="preserve">아무 관계없는 일이 우연히 동시에 일어나 억울한 의심을 받음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">감탄고토</t>
+  </si>
+  <si>
+    <t xml:space="preserve">甘呑苦吐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">토</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">달면 삼키고 쓰면 뱉는다는 뜻으로</t>
     </r>
     <r>
       <rPr>
@@ -8571,37 +8620,103 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">아무 관계없는 일이 우연히 동시에 일어나 억울한 의심을 받음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">감탄고토</t>
-  </si>
-  <si>
-    <t xml:space="preserve">甘呑苦吐</t>
-  </si>
-  <si>
-    <t xml:space="preserve">토</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">달면 삼키고 쓰면 뱉는다는 뜻으로</t>
+      <t xml:space="preserve">옳고 그름은 따지지 않고 자기에게 이로울 때만 가까이함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">견강부회</t>
+  </si>
+  <si>
+    <t xml:space="preserve">牽强附會</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">말이 안 되는 것을 억지로 끌어다 붙여 자기 말이 맞다고 우김</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">교언영색</t>
+  </si>
+  <si>
+    <t xml:space="preserve">巧言令色</t>
+  </si>
+  <si>
+    <t xml:space="preserve">색</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">남의 환심을 사려고 아첨하는 교묘한 말과 보기 좋게 꾸미는 얼굴빛</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">인물과 재능</t>
+  </si>
+  <si>
+    <t xml:space="preserve">군계일학</t>
+  </si>
+  <si>
+    <t xml:space="preserve">群鷄一鶴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">군</t>
+  </si>
+  <si>
+    <t xml:space="preserve">학</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">닭 무리 속에 서 있는 한 마리의 학처럼</t>
     </r>
     <r>
       <rPr>
@@ -8620,103 +8735,34 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">사리에 옳고 그름을 떠나 자기 비위에만 맞으면 취함</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">견강부회</t>
-  </si>
-  <si>
-    <t xml:space="preserve">牽强附會</t>
-  </si>
-  <si>
-    <t xml:space="preserve">회</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">말이 안 되는 것을 억지로 끌어다 붙여 자기 말이 맞다고 우김</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">교언영색</t>
-  </si>
-  <si>
-    <t xml:space="preserve">巧言令色</t>
-  </si>
-  <si>
-    <t xml:space="preserve">색</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">남의 환심을 사려고 아첨하는 교묘한 말과 보기 좋게 꾸미는 얼굴빛</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">인물과 재능</t>
-  </si>
-  <si>
-    <t xml:space="preserve">군계일학</t>
-  </si>
-  <si>
-    <t xml:space="preserve">群鷄一鶴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">군</t>
-  </si>
-  <si>
-    <t xml:space="preserve">학</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">닭 무리 속에 서 있는 한 마리의 학처럼</t>
+      <t xml:space="preserve">여럿 중에서 홀로 뛰어난 사람</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">화룡점정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">畵龍點睛</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">용을 그린 뒤 마지막으로 눈동자를 찍어 완성하듯</t>
     </r>
     <r>
       <rPr>
@@ -8735,34 +8781,37 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">여럿 중에서 홀로 뛰어난 사람</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">화룡점정</t>
-  </si>
-  <si>
-    <t xml:space="preserve">畵龍點睛</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">용을 그린 뒤 마지막으로 눈동자를 찍어 완성하듯</t>
+      <t xml:space="preserve">일의 가장 중요한 마지막 매듭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">금의환향</t>
+  </si>
+  <si>
+    <t xml:space="preserve">錦衣還鄕</t>
+  </si>
+  <si>
+    <t xml:space="preserve">향</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">비단옷을 입고 고향으로 돌아온다는 뜻으로</t>
     </r>
     <r>
       <rPr>
@@ -8781,37 +8830,64 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">일의 가장 중요한 마지막 매듭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">금의환향</t>
-  </si>
-  <si>
-    <t xml:space="preserve">錦衣還鄕</t>
-  </si>
-  <si>
-    <t xml:space="preserve">향</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">비단옷을 입고 고향으로 돌아온다는 뜻으로</t>
+      <t xml:space="preserve">출세하여 자랑스럽게 귀향함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">다다익선</t>
+  </si>
+  <si>
+    <t xml:space="preserve">多多益善</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">많으면 많을수록 더욱 좋음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">백전백승</t>
+  </si>
+  <si>
+    <t xml:space="preserve">百戰百勝</t>
+  </si>
+  <si>
+    <t xml:space="preserve">승</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">백 번 싸워 백 번 모두 이긴다는 뜻으로</t>
     </r>
     <r>
       <rPr>
@@ -8830,64 +8906,34 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">출세하여 자랑스럽게 귀향함</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">다다익선</t>
-  </si>
-  <si>
-    <t xml:space="preserve">多多益善</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">많으면 많을수록 더욱 좋음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">백전백승</t>
-  </si>
-  <si>
-    <t xml:space="preserve">百戰百勝</t>
-  </si>
-  <si>
-    <t xml:space="preserve">승</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">백 번 싸워 백 번 모두 이긴다는 뜻으로</t>
+      <t xml:space="preserve">모든 일에서 완벽하게 승리함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">지피지기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">知彼知己</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">적을 알고 나를 안다는 뜻으로</t>
     </r>
     <r>
       <rPr>
@@ -8906,34 +8952,37 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">모든 일에서 완벽하게 승리함</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">지피지기</t>
-  </si>
-  <si>
-    <t xml:space="preserve">知彼知己</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">적을 알고 나를 안다는 뜻으로</t>
+      <t xml:space="preserve">상대와 자신의 형편을 모두 잘 파악함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">반포지효</t>
+  </si>
+  <si>
+    <t xml:space="preserve">反哺之孝</t>
+  </si>
+  <si>
+    <t xml:space="preserve">효</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">까마귀가 자라서 늙은 어미에게 먹이를 물어다 먹이듯</t>
     </r>
     <r>
       <rPr>
@@ -8952,37 +9001,37 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">상대와 자신의 형편을 모두 잘 파악함</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">반포지효</t>
-  </si>
-  <si>
-    <t xml:space="preserve">反哺之孝</t>
-  </si>
-  <si>
-    <t xml:space="preserve">효</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">까마귀가 자라서 늙은 어미에게 먹이를 물어다 먹이듯</t>
+      <t xml:space="preserve">부모의 은혜에 보답하는 지극한 효도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">결초보은</t>
+  </si>
+  <si>
+    <t xml:space="preserve">結草報恩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">은</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">풀을 묶어서라도 은혜를 갚는다는 뜻으로</t>
     </r>
     <r>
       <rPr>
@@ -9001,37 +9050,64 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">부모의 은혜에 보답하는 지극한 효도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">결초보은</t>
-  </si>
-  <si>
-    <t xml:space="preserve">結草報恩</t>
-  </si>
-  <si>
-    <t xml:space="preserve">은</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">풀을 묶어서라도 은혜를 갚는다는 뜻으로</t>
+      <t xml:space="preserve">죽어서도 은혜를 잊지 않고 갚음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">선견지명</t>
+  </si>
+  <si>
+    <t xml:space="preserve">先見之明</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">어떤 일이 일어나기 전에 앞을 미리 내다보는 뛰어난 지혜와 안목</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">쾌도난마</t>
+  </si>
+  <si>
+    <t xml:space="preserve">快刀亂麻</t>
+  </si>
+  <si>
+    <t xml:space="preserve">쾌</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">잘 드는 칼로 엉클어진 삼을 자르듯</t>
     </r>
     <r>
       <rPr>
@@ -9050,64 +9126,127 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">죽어서도 은혜를 잊지 않고 갚음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">선견지명</t>
-  </si>
-  <si>
-    <t xml:space="preserve">先見之明</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">어떤 일이 일어나기 전에 앞을 미리 내다보는 뛰어난 지혜와 안목</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">쾌도난마</t>
-  </si>
-  <si>
-    <t xml:space="preserve">快刀亂麻</t>
-  </si>
-  <si>
-    <t xml:space="preserve">쾌</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">잘 드는 칼로 엉클어진 삼을 자르듯</t>
+      <t xml:space="preserve">복잡한 일이나 분쟁을 명쾌하게 해결함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">학수고대</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鶴首苦待</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">학의 목처럼 목을 길게 빼고 간절하게 기다림</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">맹모삼천</t>
+  </si>
+  <si>
+    <t xml:space="preserve">孟母三遷</t>
+  </si>
+  <si>
+    <t xml:space="preserve">맹</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">맹자의 어머니가 자녀의 교육을 위하여 세 번이나 집을 옮김</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">괄목상대</t>
+  </si>
+  <si>
+    <t xml:space="preserve">刮目相對</t>
+  </si>
+  <si>
+    <t xml:space="preserve">괄</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">눈을 비비고 상대편을 다시 볼 만큼 남의 학식이나 재주가 깜짝 놀랄 만큼 발전함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">낭중지추</t>
+  </si>
+  <si>
+    <t xml:space="preserve">囊中之錐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">낭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">추</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주머니 속의 송곳처럼</t>
     </r>
     <r>
       <rPr>
@@ -9126,127 +9265,94 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">복잡한 일이나 분쟁을 명쾌하게 해결함</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">학수고대</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鶴首苦待</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">학의 목처럼 목을 길게 빼고 간절하게 기다림</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">맹모삼천</t>
-  </si>
-  <si>
-    <t xml:space="preserve">孟母三遷</t>
-  </si>
-  <si>
-    <t xml:space="preserve">맹</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">맹자의 어머니가 자녀의 교육을 위하여 세 번이나 집을 옮김</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">괄목상대</t>
-  </si>
-  <si>
-    <t xml:space="preserve">刮目相對</t>
-  </si>
-  <si>
-    <t xml:space="preserve">괄</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">눈을 비비고 상대편을 다시 볼 만큼 남의 학식이나 재주가 깜짝 놀랄 만큼 발전함</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">낭중지추</t>
-  </si>
-  <si>
-    <t xml:space="preserve">囊中之錐</t>
-  </si>
-  <si>
-    <t xml:space="preserve">낭</t>
-  </si>
-  <si>
-    <t xml:space="preserve">추</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">주머니 속의 송곳처럼</t>
+      <t xml:space="preserve">뛰어난 재능을 가진 사람은 숨어 있어도 저절로 드러남</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">풍수지탄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">風樹之嘆</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">효도를 다하려 하나 이미 부모가 돌아가셔서 효도할 길이 없음을 탄식함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">화합과 표현</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이구동성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">異口同聲</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입은 서로 다르지만 모두 똑같은 목소리로 한마디로 말함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">동문서답</t>
+  </si>
+  <si>
+    <t xml:space="preserve">東問西答</t>
+  </si>
+  <si>
+    <t xml:space="preserve">답</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">동쪽을 묻는데 서쪽을 답하듯</t>
     </r>
     <r>
       <rPr>
@@ -9265,94 +9371,70 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">뛰어난 재능을 가진 사람은 숨어 있어도 저절로 드러남</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">풍수지탄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">風樹之嘆</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">효도를 다하려 하나 이미 부모가 돌아가셔서 효도할 길이 없음을 탄식함</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">화합과 표현</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이구동성</t>
-  </si>
-  <si>
-    <t xml:space="preserve">異口同聲</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">입은 서로 다르지만 모두 똑같은 목소리로 한마디로 말함</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">동문서답</t>
-  </si>
-  <si>
-    <t xml:space="preserve">東問西答</t>
-  </si>
-  <si>
-    <t xml:space="preserve">답</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">동쪽을 묻는데 서쪽을 답하듯</t>
+      <t xml:space="preserve">질문과 전혀 상관없는 엉뚱한 대답을 함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">횡설수설</t>
+  </si>
+  <si>
+    <t xml:space="preserve">橫說竪說</t>
+  </si>
+  <si>
+    <t xml:space="preserve">횡</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">앞뒤가 맞지 않게 말을 이리저리 늘어놓음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">자연과 계절</t>
+  </si>
+  <si>
+    <t xml:space="preserve">천고마비</t>
+  </si>
+  <si>
+    <t xml:space="preserve">天高馬肥</t>
+  </si>
+  <si>
+    <t xml:space="preserve">비</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">하늘은 높고 푸르며 말은 살찐다는 뜻으로</t>
     </r>
     <r>
       <rPr>
@@ -9371,70 +9453,181 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">질문과 전혀 상관없는 엉뚱한 대답을 함</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">횡설수설</t>
-  </si>
-  <si>
-    <t xml:space="preserve">橫說竪說</t>
-  </si>
-  <si>
-    <t xml:space="preserve">횡</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">조리가 없이 말을 이리저리 두서없이 마구 늘어놓음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">자연과 계절</t>
-  </si>
-  <si>
-    <t xml:space="preserve">천고마비</t>
-  </si>
-  <si>
-    <t xml:space="preserve">天高馬肥</t>
-  </si>
-  <si>
-    <t xml:space="preserve">비</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">하늘은 높고 푸르며 말은 살찐다는 뜻으로</t>
+      <t xml:space="preserve">풍요롭고 아름다운 가을철을 이름</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">화기애애</t>
+  </si>
+  <si>
+    <t xml:space="preserve">和氣靄靄</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">화목하고 따뜻한 기운이 넘쳐흘러 분위기가 무척 부드러움</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">태평연월</t>
+  </si>
+  <si>
+    <t xml:space="preserve">太平烟月</t>
+  </si>
+  <si>
+    <t xml:space="preserve">월</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">세상이 평화롭고 사람들이 편안하게 잘 사는 시절</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">어부지리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">漁父之利</t>
+  </si>
+  <si>
+    <t xml:space="preserve">리</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">두 사람이 다투는 사이에 제삼자가 힘들이지 않고 이익을 차지함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">유유상종</t>
+  </si>
+  <si>
+    <t xml:space="preserve">類類相從</t>
+  </si>
+  <si>
+    <t xml:space="preserve">종</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">같은 무리나 비슷한 성향을 가진 사람끼리 서로 잘 어울림</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">오매불망</t>
+  </si>
+  <si>
+    <t xml:space="preserve">寤寐不忘</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자나 깨나 잊지 못하고 항상 마음속 깊이 생각함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">호가호위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">狐假虎威</t>
+  </si>
+  <si>
+    <t xml:space="preserve">위</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">여우가 호랑이의 힘을 빌려 다른 짐승을 겁주듯</t>
     </r>
     <r>
       <rPr>
@@ -9453,181 +9646,181 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">풍요롭고 아름다운 가을철을 이름</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">화기애애</t>
-  </si>
-  <si>
-    <t xml:space="preserve">和氣靄靄</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">화목하고 따뜻한 기운이 넘쳐흘러 분위기가 무척 부드러움</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">태평연월</t>
-  </si>
-  <si>
-    <t xml:space="preserve">太平烟月</t>
-  </si>
-  <si>
-    <t xml:space="preserve">월</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">세상이 평화롭고 사람들이 편안하게 잘 사는 시절</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">어부지리</t>
-  </si>
-  <si>
-    <t xml:space="preserve">漁父之利</t>
-  </si>
-  <si>
-    <t xml:space="preserve">리</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">두 사람이 다투는 사이에 제삼자가 힘들이지 않고 이익을 차지함</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">유유상종</t>
-  </si>
-  <si>
-    <t xml:space="preserve">類類相從</t>
-  </si>
-  <si>
-    <t xml:space="preserve">종</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">같은 무리나 비슷한 성향을 가진 사람끼리 서로 잘 어울림</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">오매불망</t>
-  </si>
-  <si>
-    <t xml:space="preserve">寤寐不忘</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">자나 깨나 잊지 못하고 항상 마음속 깊이 생각함</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">호가호위</t>
-  </si>
-  <si>
-    <t xml:space="preserve">狐假虎威</t>
-  </si>
-  <si>
-    <t xml:space="preserve">위</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">여우가 호랑이의 위세를 빌려 남을 위협하듯</t>
+      <t xml:space="preserve">남의 힘을 등에 업고 뽐냄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">두문불출</t>
+  </si>
+  <si>
+    <t xml:space="preserve">杜門不出</t>
+  </si>
+  <si>
+    <t xml:space="preserve">출</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">문을 닫아걸고 집 밖으로 나가지 않으며 세상과 인연을 끊음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">차일피일</t>
+  </si>
+  <si>
+    <t xml:space="preserve">此日彼日</t>
+  </si>
+  <si>
+    <t xml:space="preserve">차</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이날 저날 하며 기한이나 약속을 자꾸 뒤로 미룸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">우유부단</t>
+  </si>
+  <si>
+    <t xml:space="preserve">優柔不斷</t>
+  </si>
+  <si>
+    <t xml:space="preserve">단</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">우물쭈물하며 똑 부러지게 결단을 내리지 못함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">부화뇌동</t>
+  </si>
+  <si>
+    <t xml:space="preserve">附和雷同</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자기 생각 없이 남이 하는 대로 덩달아 따라 함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">천생연분</t>
+  </si>
+  <si>
+    <t xml:space="preserve">天生緣分</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">하늘이 정해 준 피할 수 없는 깊고 아름다운 인연</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">오리무중</t>
+  </si>
+  <si>
+    <t xml:space="preserve">五里霧中</t>
+  </si>
+  <si>
+    <t xml:space="preserve">중</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">오 리나 짙은 안개 속에 갇힌 듯</t>
     </r>
     <r>
       <rPr>
@@ -9646,181 +9839,34 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">남의 권세를 빌려 위세를 부림</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">두문불출</t>
-  </si>
-  <si>
-    <t xml:space="preserve">杜門不出</t>
-  </si>
-  <si>
-    <t xml:space="preserve">출</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">문을 닫아걸고 집 밖으로 나가지 않으며 세상과 인연을 끊음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">차일피일</t>
-  </si>
-  <si>
-    <t xml:space="preserve">此日彼日</t>
-  </si>
-  <si>
-    <t xml:space="preserve">차</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이날 저날 하며 기한이나 약속을 자꾸 뒤로 미룸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">우유부단</t>
-  </si>
-  <si>
-    <t xml:space="preserve">優柔不斷</t>
-  </si>
-  <si>
-    <t xml:space="preserve">단</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">우물쭈물하며 똑 부러지게 결단을 내리지 못함</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">부화뇌동</t>
-  </si>
-  <si>
-    <t xml:space="preserve">附和雷同</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">뚜렷한 소신 없이 남의 의견이나 행동에 덩달아 맹목적으로 따름</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">천생연분</t>
-  </si>
-  <si>
-    <t xml:space="preserve">天生緣分</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">하늘이 정해 준 피할 수 없는 깊고 아름다운 인연</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">오리무중</t>
-  </si>
-  <si>
-    <t xml:space="preserve">五里霧中</t>
-  </si>
-  <si>
-    <t xml:space="preserve">중</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">오 리나 짙은 안개 속에 갇힌 듯</t>
+      <t xml:space="preserve">일의 갈피를 잡을 수 없고 방향이 묘연함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">화중지병</t>
+  </si>
+  <si>
+    <t xml:space="preserve">畵中之餠</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그림의 떡이라는 뜻으로</t>
     </r>
     <r>
       <rPr>
@@ -9839,34 +9885,94 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">일의 갈피를 잡을 수 없고 방향이 묘연함</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">화중지병</t>
-  </si>
-  <si>
-    <t xml:space="preserve">畵中之餠</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">그림의 떡이라는 뜻으로</t>
+      <t xml:space="preserve">바라만 볼 뿐 결코 이용하거나 차지할 수 없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">함흥차사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">咸興差使</t>
+  </si>
+  <si>
+    <t xml:space="preserve">함</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">심부름을 간 사람이 한 번 가서 소식이 아주 없거나 돌아오지 않음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">삼고초려</t>
+  </si>
+  <si>
+    <t xml:space="preserve">三顧草廬</t>
+  </si>
+  <si>
+    <t xml:space="preserve">삼</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인재를 정성껏 맞아들이기 위해 초가집을 세 번이나 찾아감</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">배수지진</t>
+  </si>
+  <si>
+    <t xml:space="preserve">背水之陣</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">강물을 등지고 진을 쳐서 물러설 곳을 없앤다는 뜻으로</t>
     </r>
     <r>
       <rPr>
@@ -9885,94 +9991,34 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">바라만 볼 뿐 결코 이용하거나 차지할 수 없음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">함흥차사</t>
-  </si>
-  <si>
-    <t xml:space="preserve">咸興差使</t>
-  </si>
-  <si>
-    <t xml:space="preserve">함</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">심부름을 간 사람이 한 번 가서 소식이 아주 없거나 돌아오지 않음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">삼고초려</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三顧草廬</t>
-  </si>
-  <si>
-    <t xml:space="preserve">삼</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인재를 정성껏 맞아들이기 위해 초가집을 세 번이나 찾아감</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">배수지진</t>
-  </si>
-  <si>
-    <t xml:space="preserve">背水之陣</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">물을 등지고 진을 치듯</t>
+      <t xml:space="preserve">더는 물러서지 않겠다는 각오로 온 힘을 다함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">일사천리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一瀉千里</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">물이 거침없이 쏟아져 천 리를 흐르듯</t>
     </r>
     <r>
       <rPr>
@@ -9991,34 +10037,34 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">목숨을 걸고 물러설 곳 없이 필사적으로 싸움</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">일사천리</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一瀉千里</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">물이 거침없이 쏟아져 천 리를 흐르듯</t>
+      <t xml:space="preserve">일이 막힘없이 단숨에 진행됨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">일망타진</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一網打盡</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">한 번 그물을 쳐서 물고기를 다 잡듯</t>
     </r>
     <r>
       <rPr>
@@ -10037,34 +10083,34 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">일이 막힘없이 단숨에 진행됨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">일망타진</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一網打盡</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">한 번 그물을 쳐서 물고기를 다 잡듯</t>
+      <t xml:space="preserve">무리나 적을 한 번에 모조리 잡아들임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">파란만장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">波瀾萬丈</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2A26"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">물결이 만 길이나 높이 일듯</t>
     </r>
     <r>
       <rPr>
@@ -10083,52 +10129,6 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">무리나 적을 한 번에 모조리 잡아들임</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">파란만장</t>
-  </si>
-  <si>
-    <t xml:space="preserve">波瀾萬丈</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">물결이 만 길이나 높이 일듯</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2A26"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">일이나 인생의 우여곡절과 변화가 심함</t>
     </r>
     <r>
@@ -10146,7 +10146,7 @@
     <t xml:space="preserve">요지부동</t>
   </si>
   <si>
-    <t xml:space="preserve">搖之不動</t>
+    <t xml:space="preserve">搖之不動</t>
   </si>
   <si>
     <r>
@@ -10210,7 +10210,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">어디에도 아무런 쓸모가 없는 물건이나 사람</t>
+      <t xml:space="preserve">아무 데도 쓸 곳이 없는 물건</t>
     </r>
     <r>
       <rPr>
@@ -34990,7 +34990,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="30" t="n">
         <v>65</v>
       </c>
@@ -35276,7 +35276,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="30" t="n">
         <v>76</v>
       </c>
@@ -35406,7 +35406,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="30" t="n">
         <v>81</v>
       </c>
@@ -36784,7 +36784,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="30" t="n">
         <v>134</v>
       </c>
